--- a/钓鱼玩法固定数值表.xlsx
+++ b/钓鱼玩法固定数值表.xlsx
@@ -22,7 +22,8 @@
     <sheet name="rods" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="baits" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="vessels" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="spot_clues" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="spot_clue_texts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="spot_tags" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,32 +503,90 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>线索ID
+唯一主键。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>线索类型
+habitat 鱼喜环境 / activity 鱼情观察。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>线索文案
+坐席后聊天气泡展示的中文。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>权重
+加权随机相对权重，默认 1。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>最低钓鱼等级
+未达到不进入抽选池。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>最低塘熟练度
+未达到不进入抽选池。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>塘分级过滤
+空=全塘；否则仅匹配该分级。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>点位标签过滤
+空=不限；与 spot_tags.tags 命中任一即可。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>鱼种备注
+策划备注，UI 可不显示。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>是否启用
+FALSE 不参与抽选。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>策划</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>鱼塘ID
-线索所属塘。</t>
+点位所属塘。</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>钓点ID
-点位主键。</t>
+与运行时 spotId 对齐。</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>最低钓鱼等级
-未达到不显示该线索。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>最低塘等级
-未达到不显示该线索。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>线索文案
-悬停/靠近时显示的中文。</t>
+        <t>标签列表
+逗号分隔，如 weed,shade。</t>
       </text>
     </comment>
   </commentList>
@@ -1203,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3349,110 +3408,286 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>spot_clues</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>clueId</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>线索ID</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>线索所属塘。</t>
+          <t>唯一主键。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>spot_clues</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>spotId</t>
+          <t>clueType</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>钓点ID</t>
+          <t>线索类型</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>点位主键。</t>
+          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>spot_clues</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>clueText</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>最低钓鱼等级</t>
+          <t>线索文案</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>未达到不显示该线索。</t>
+          <t>坐席后聊天气泡展示的中文。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>spot_clues</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>minPondLevel</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>最低塘等级</t>
+          <t>权重</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>未达到不显示该线索。</t>
+          <t>加权随机相对权重，默认 1。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>spot_clues</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>clueText</t>
+          <t>minPlayerLevel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>线索文案</t>
+          <t>最低钓鱼等级</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>悬停/靠近时显示的中文。</t>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>minPondLevel</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>最低塘熟练度</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>pondCategory</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>塘分级过滤</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>空=全塘；否则仅匹配该分级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>spotTag</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>点位标签过滤</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>空=不限；与 spot_tags.tags 命中任一即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>speciesHint</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>鱼种备注</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>策划备注，UI 可不显示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>FALSE 不参与抽选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>鱼塘ID</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>点位所属塘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>spotId</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>钓点ID</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>与运行时 spotId 对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>标签列表</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>逗号分隔，如 weed,shade。</t>
         </is>
       </c>
     </row>
@@ -5116,113 +5351,1341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>clueId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>spotId</t>
+          <t>clueType</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>clueText</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>minPlayerLevel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>minPondLevel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>clueText</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pondCategory</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>spotTag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>speciesHint</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>线索ID</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>钓点ID</t>
+          <t>线索类型</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>线索文案</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>最低钓鱼等级</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>最低塘等级</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>线索文案</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>最低塘熟练度</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>塘分级过滤</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>点位标签过滤</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>鱼种备注</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>是否启用</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pond-calm</t>
+          <t>h-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>spot-1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>鲫鱼爱往草缝和凹岸钻，亮水中央往往不是它们的主场。</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>这片水很清澈</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>crucian</t>
+        </is>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>h-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>「鲤鱼钓凸，鲫鱼钓凹」——凹湾浅草边，常是板鲫爱转的地方。</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>crucian</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>h-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>进水口附近溶氧足、食物多，鲫鲤都爱在缓流一侧停留。</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>inlet</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>crucian,carp</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>h-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>树荫弱光处更对鲤鱼胃口，大晴天它们不爱长时间晒在亮水。</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>shade</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>carp</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>h-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>深浅交界、沟坎斜坡像「鱼道」，鲤鱼常沿这些结构巡游。</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>carp</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>h-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>乱石、木桩、桥墩旁藏食又藏身，鲤鱼、鲶类都可能路过。</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>carp</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>h-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>草鱼爱贴草缘和芦苇空隙活动，岸边有果树、庄稼的一侧更香。</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>grass</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>h-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>大坝拐角、洄水湾流速缓，草青一类大鱼爱在这里歇脚。</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>inlet</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>grass</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>h-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>水色清中带浊才宜钓；清澈见底往往反而难有大货久留。</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>h-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>水像泥浆看不清饵，鱼也难开口——过浑的点要谨慎。</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>muddy</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>h-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>下风口容易聚浮游饵和氧气，夏秋很多鱼喜欢贴着风口转。</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>inlet</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>h-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>夏钓荫、夏钓深：大太阳时树荫或略深处，比浅滩更稳妥。</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>shade</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>h-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>洄湾里食物沉降、水流缓和，杂食鱼常来这里觅食。</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>inlet</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>carp,crucian</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>h-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>水草太密又无啃食痕迹，未必有草鱼；倒可能藏着小鲫在缝里。</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>crucian</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>h-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>habitat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>铧尖、凸嘴延伸进大水面，像鲤鱼通勤必经的「路口」。</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>carp</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>水面死寂如镜、半天不起波，多半开口差，或鱼不在这层活动。</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>a-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>偶尔有鱼花、涟漪，说明这片水里还有活性，值得守一阵。</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>a-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>细密成串的小泡像断了的珍珠，老钓友常当鲫鱼星来看。</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>a-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>一大片杂乱气泡夹着浑浊，像锅底翻开——很像鲤鱼在拱泥。</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>muddy</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>a-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>突兀冒出的大单泡、啪一下散掉，草边出现时要当心草鱼路过。</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>位置固定、大小均匀、节奏死板的泡，更像沼气泡，别当鱼星。</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>a-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>水草残缺、只剩茎秆，说明有鱼在啃，草鳊类可能性上升。</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>草叶轻轻摇，未必是大风——有时是鱼在草下拱食。</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>小杂鱼在边子窜，深处未必没货，但闹窝时要有心理准备。</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>a-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>能闻到淡淡腥气、听见远处啪水，说明这片水域并不空。</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>a-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>鱼群长时间浮头嚼水，多是缺氧，硬钓往往白费力气。</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>a-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>人影一晃鱼就炸窝逃窜，说明这里刚受惊，先缓一缓再落饵。</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>a-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>星泡跟着移动、大小不一，比「定点死泡」更像活鱼在觅食。</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>a-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>窝边星泡突然变密变快，常是鱼群进窝、活性上来了。</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>水色发绿过肥时，鱼饱腹懒开口，鱼情会显得「闷」。</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>spotId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>鱼塘ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>钓点ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>标签列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>pond-calm</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>calm-spot-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>clear,weed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pond-calm</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>spot-2</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>这边水草很多</t>
+          <t>calm-spot-2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>weed,shade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pond-calm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>calm-spot-3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pond-calm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>calm-spot-4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pond-calm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>calm-spot-5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>muddy</t>
         </is>
       </c>
     </row>

--- a/钓鱼玩法固定数值表.xlsx
+++ b/钓鱼玩法固定数值表.xlsx
@@ -11,19 +11,20 @@
     <sheet name="_meta" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ponds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="player_levels" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="pond_levels" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="fish_species" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="fish_xp" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="fish_sell" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="pond_modifiers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="pond_fish_pool" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="pond_quality_cap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="pond_fish_size_cap" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="rods" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="baits" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="vessels" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="spot_clue_texts" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="spot_tags" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="return_rules" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="pond_levels" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="fish_species" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="fish_xp" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="fish_sell" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="pond_modifiers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="pond_fish_pool" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="pond_quality_cap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="pond_fish_size_cap" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="rods" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="baits" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="vessels" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="spot_clue_texts" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="spot_tags" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,6 +191,46 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>鱼塘ID
+该塘可出的鱼。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>鱼种ID
+库存模板条目。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>角色
+common 常驻 / rare 稀有。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>刷新权重
+相对权重。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>是否启用
+FALSE 则该条不参与刷新。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>策划</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>鱼塘ID
 品质软帽。</t>
       </text>
     </comment>
@@ -215,7 +256,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -255,7 +296,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -385,7 +426,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -449,7 +490,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -495,7 +536,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -565,7 +606,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment17.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -717,6 +758,70 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>最低品质
+低于此品质不可回鱼；gray=灰及以上。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>最小体长比
+相对品质最大体长的下限，如 0.2。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>最大体长比
+相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>回鱼金倍率
+回鱼金 = floor(卖价 × 本倍率)，建议 0.70。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>玩家经验
+每次回鱼发给玩家的熟练度。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>鱼塘经验
+每次回鱼发给当前塘熟练度。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>增重下限m
+塘内实体增重下限。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>增重上限m
+塘内实体增重上限。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>增重模式
+uniform_random=区间均匀随机。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>策划</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>鱼塘等级
 1~10。</t>
       </text>
@@ -731,7 +836,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -777,7 +882,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -817,7 +922,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -863,7 +968,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -927,46 +1032,6 @@
       <text>
         <t>出警时限毫秒
 时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>策划</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>鱼塘ID
-该塘可出的鱼。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>鱼种ID
-库存模板条目。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>角色
-common 常驻 / rare 稀有。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>刷新权重
-相对权重。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>是否启用
-FALSE 则该条不参与刷新。</t>
       </text>
     </comment>
   </commentList>
@@ -1262,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1692,616 +1757,616 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pond_levels</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>minQuality</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>鱼塘等级</t>
+          <t>最低品质</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1~10。</t>
+          <t>低于此品质不可回鱼；gray=灰及以上。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pond_levels</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>xpToNext</t>
+          <t>minSizeRatio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>升到下级所需塘经验</t>
+          <t>最小体长比</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10 级为 0。</t>
+          <t>相对品质最大体长的下限，如 0.2。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>maxSizeRatio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>最大体长比</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>goldMulVsSell</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>回鱼金倍率</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>商店/图鉴显示。</t>
+          <t>回鱼金 = floor(卖价 × 本倍率)，建议 0.70。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>食性</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>每次回鱼发给玩家的熟练度。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>catchGroup</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>钓组</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
+          <t>每次回鱼发给当前塘熟练度。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>typicalMinM</t>
+          <t>sizeGainMinM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>典型最小体长m</t>
+          <t>增重下限m</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>展示参考，不是硬帽。</t>
+          <t>塘内实体增重下限。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>typicalMaxM</t>
+          <t>sizeGainMaxM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>典型最大体长m</t>
+          <t>增重上限m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>展示参考，不是硬帽。</t>
+          <t>塘内实体增重上限。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>sizeGainMode</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>增重模式</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>与 fish_species 对齐。</t>
+          <t>uniform_random=区间均匀随机。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>pond_levels</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>speciesName</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>鱼塘等级</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>便于策划阅读。</t>
+          <t>1~10。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>pond_levels</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>xpToNext</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>升到下级所需塘经验</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gray/green/blue/purple/red/orange/gold。</t>
+          <t>10 级为 0。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>playerXp</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>玩家经验</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>钓上该品质该种鱼给玩家的经验。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pondXp</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>鱼塘经验</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>同时给当前塘熟练度的经验。</t>
+          <t>商店/图鉴显示。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>食性</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>卖价品质底表；空行表示下面是钓组系数。</t>
+          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QUALITY_BASE</t>
+          <t>catchGroup</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>品质底价</t>
+          <t>钓组</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>卖价公式底数。</t>
+          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SIZE_REF</t>
+          <t>typicalMinM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>体长参考m</t>
+          <t>典型最小体长m</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>卖价公式尺寸归一化。</t>
+          <t>展示参考，不是硬帽。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MIN_SELL</t>
+          <t>typicalMaxM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>最低卖价</t>
+          <t>典型最大体长m</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>向下取整后的保底。</t>
+          <t>展示参考，不是硬帽。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>catchGroup</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>钓组</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SPECIES_MULT 所对应的钓组。</t>
+          <t>与 fish_species 对齐。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SPECIES_MULT</t>
+          <t>speciesName</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>钓组卖价系数</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>乘在品质底价上。</t>
+          <t>便于策划阅读。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>鱼塘分级</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>与 ponds.pondCategory 对应。</t>
+          <t>gray/green/blue/purple/red/orange/gold。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>biteRateMul</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>咬钩倍率</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>塘级对咬钩率的乘区。</t>
+          <t>钓上该品质该种鱼给玩家的经验。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>escapeRateMul</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>脱钩倍率</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>塘级对脱钩率的乘区。</t>
+          <t>同时给当前塘熟练度的经验。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>infoRevealMul</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>信息揭示倍率</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>线索/信息量。</t>
+          <t>卖价品质底表；空行表示下面是钓组系数。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>qualityWeightSkew</t>
+          <t>QUALITY_BASE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>品质权重倾斜</t>
+          <t>品质底价</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>&gt;1 偏向高品质。</t>
+          <t>卖价公式底数。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sizeCapMul</t>
+          <t>SIZE_REF</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>体长上限倍率</t>
+          <t>体长参考m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>乘在鱼种尺寸帽上。</t>
+          <t>卖价公式尺寸归一化。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pondXpMul</t>
+          <t>MIN_SELL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>塘经验倍率</t>
+          <t>最低卖价</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>该分级塘熟练度获取。</t>
+          <t>向下取整后的保底。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fineChancePerHour</t>
+          <t>catchGroup</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>每小时出警概率</t>
+          <t>钓组</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
+          <t>SPECIES_MULT 所对应的钓组。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fineGold</t>
+          <t>SPECIES_MULT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>超时罚款金币</t>
+          <t>钓组卖价系数</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
+          <t>乘在品质底价上。</t>
         </is>
       </c>
     </row>
@@ -2313,222 +2378,222 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>policeWarningMs</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>出警时限毫秒</t>
+          <t>鱼塘分级</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
+          <t>与 ponds.pondCategory 对应。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>biteRateMul</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>咬钩倍率</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>该塘可出的鱼。</t>
+          <t>塘级对咬钩率的乘区。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>escapeRateMul</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>脱钩倍率</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>库存模板条目。</t>
+          <t>塘级对脱钩率的乘区。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>infoRevealMul</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>信息揭示倍率</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>common 常驻 / rare 稀有。</t>
+          <t>线索/信息量。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>spawnWeight</t>
+          <t>qualityWeightSkew</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>刷新权重</t>
+          <t>品质权重倾斜</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>相对权重。</t>
+          <t>&gt;1 偏向高品质。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>sizeCapMul</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>体长上限倍率</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FALSE 则该条不参与刷新。</t>
+          <t>乘在鱼种尺寸帽上。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>pondXpMul</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>塘经验倍率</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>品质软帽。</t>
+          <t>该分级塘熟练度获取。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>minQuality</t>
+          <t>fineChancePerHour</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>最低品质</t>
+          <t>每小时出警概率</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>该塘随机品质下限。</t>
+          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>maxQuality</t>
+          <t>fineGold</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>最高品质</t>
+          <t>超时罚款金币</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>该塘随机品质上限。</t>
+          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>policeWarningMs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>出警时限毫秒</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>策划说明，不进规则。</t>
+          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2543,14 +2608,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>体长硬帽。</t>
+          <t>该塘可出的鱼。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2565,271 +2630,271 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>该塘该种鱼。</t>
+          <t>库存模板条目。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>按品质分档的尺寸帽。</t>
+          <t>common 常驻 / rare 稀有。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>minSizeM</t>
+          <t>spawnWeight</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>最小体长m</t>
+          <t>刷新权重</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>随机体长下限。</t>
+          <t>相对权重。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>maxSizeM</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>最大体长m</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>随机体长上限。</t>
+          <t>FALSE 则该条不参与刷新。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>rodId</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>钓竿ID</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>程序主键，商店与装备用。</t>
+          <t>品质软帽。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>minQuality</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>最低品质</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>该塘随机品质下限。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>subType</t>
+          <t>maxQuality</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>竿型</t>
+          <t>最高品质</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
+          <t>该塘随机品质上限。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0 表示新手赠送，商店不可回购。</t>
+          <t>策划说明，不进规则。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>biteBonus</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>咬钩加成</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
+          <t>体长硬帽。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>escapeReduction</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>防脱</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
+          <t>该塘该种鱼。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>breakSizeM</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>超规格体长m</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>成功钓上大于该体长的鱼计入超规格。</t>
+          <t>按品质分档的尺寸帽。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>breakMaxLandings</t>
+          <t>minSizeM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>超规格成功上限</t>
+          <t>最小体长m</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
+          <t>随机体长下限。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>fitGray</t>
+          <t>maxSizeM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>灰品质适配</t>
+          <t>最大体长m</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
+          <t>随机体长上限。</t>
         </is>
       </c>
     </row>
@@ -2841,17 +2906,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>fitGreen</t>
+          <t>rodId</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>绿品质适配</t>
+          <t>钓竿ID</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>程序主键，商店与装备用。</t>
         </is>
       </c>
     </row>
@@ -2863,17 +2928,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>fitBlue</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>蓝品质适配</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -2885,17 +2950,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fitPurple</t>
+          <t>subType</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>紫品质适配</t>
+          <t>竿型</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
         </is>
       </c>
     </row>
@@ -2907,17 +2972,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fitRed</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>红品质适配</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>0 表示新手赠送，商店不可回购。</t>
         </is>
       </c>
     </row>
@@ -2929,17 +2994,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fitOrange</t>
+          <t>biteBonus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>橙品质适配</t>
+          <t>咬钩加成</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
         </is>
       </c>
     </row>
@@ -2951,17 +3016,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fitGold</t>
+          <t>escapeReduction</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>金品质适配</t>
+          <t>防脱</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
         </is>
       </c>
     </row>
@@ -2973,17 +3038,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fitStillBait</t>
+          <t>breakSizeM</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>静水底钓适配</t>
+          <t>超规格体长m</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>对应 catchGroup=still_bait。</t>
+          <t>成功钓上大于该体长的鱼计入超规格。</t>
         </is>
       </c>
     </row>
@@ -2995,17 +3060,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fitStreamLight</t>
+          <t>breakMaxLandings</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>溪流轻口适配</t>
+          <t>超规格成功上限</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>对应 catchGroup=stream_light。</t>
+          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
         </is>
       </c>
     </row>
@@ -3017,17 +3082,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fitLurePredator</t>
+          <t>fitGray</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>路亚掠食适配</t>
+          <t>灰品质适配</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>对应 catchGroup=lure_predator。</t>
+          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3104,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fitCastHeavy</t>
+          <t>fitGreen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>重抛适配</t>
+          <t>绿品质适配</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>对应 catchGroup=cast_heavy。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
@@ -3061,232 +3126,232 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fitGiantGame</t>
+          <t>fitBlue</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>巨物适配</t>
+          <t>蓝品质适配</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>对应 catchGroup=giant_game。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>baitId</t>
+          <t>fitPurple</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>鱼饵ID</t>
+          <t>紫品质适配</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>fitRed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>红品质适配</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>fitOrange</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>对口食性</t>
+          <t>橙品质适配</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>fitGold</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>金品质适配</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0 表示开局可用。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>costGoldPerUse</t>
+          <t>fitStillBait</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>每次扣金</t>
+          <t>静水底钓适配</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
+          <t>对应 catchGroup=still_bait。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>biteBonusHerbivore</t>
+          <t>fitStreamLight</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>对草食咬钩加成</t>
+          <t>溪流轻口适配</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>对应 catchGroup=stream_light。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>biteBonusOmnivore</t>
+          <t>fitLurePredator</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>对杂食咬钩加成</t>
+          <t>路亚掠食适配</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>对应 catchGroup=lure_predator。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>biteBonusCarnivore</t>
+          <t>fitCastHeavy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>对肉食咬钩加成</t>
+          <t>重抛适配</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>如 0.07 = +7%。</t>
+          <t>对应 catchGroup=cast_heavy。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>isDefaultInfinite</t>
+          <t>fitGiantGame</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>是否无限基础饵</t>
+          <t>巨物适配</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TRUE 的饵永不短缺，也不扣金。</t>
+          <t>对应 catchGroup=giant_game。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>vesselId</t>
+          <t>baitId</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>船具ID</t>
+          <t>鱼饵ID</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3298,7 +3363,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3320,286 +3385,286 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>对口食性</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>低于此等级不能买。</t>
+          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一次性购入。</t>
+          <t>0 表示开局可用。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>placeholderCatchCount</t>
+          <t>costGoldPerUse</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>占位捕捞次数</t>
+          <t>每次扣金</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>表内预留，当前不生效。</t>
+          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>enabledUse</t>
+          <t>biteBonusHerbivore</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>是否允许使用</t>
+          <t>对草食咬钩加成</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FALSE：可买但不可装备、不可开船。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>clueId</t>
+          <t>biteBonusOmnivore</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>线索ID</t>
+          <t>对杂食咬钩加成</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>唯一主键。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>clueType</t>
+          <t>biteBonusCarnivore</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>线索类型</t>
+          <t>对肉食咬钩加成</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
+          <t>如 0.07 = +7%。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>clueText</t>
+          <t>isDefaultInfinite</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>线索文案</t>
+          <t>是否无限基础饵</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>坐席后聊天气泡展示的中文。</t>
+          <t>TRUE 的饵永不短缺，也不扣金。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>vesselId</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>船具ID</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>加权随机相对权重，默认 1。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>最低钓鱼等级</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>minPondLevel</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>最低塘熟练度</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>低于此等级不能买。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>pondCategory</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>塘分级过滤</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>空=全塘；否则仅匹配该分级。</t>
+          <t>一次性购入。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>spotTag</t>
+          <t>placeholderCatchCount</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>点位标签过滤</t>
+          <t>占位捕捞次数</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>空=不限；与 spot_tags.tags 命中任一即可。</t>
+          <t>表内预留，当前不生效。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>speciesHint</t>
+          <t>enabledUse</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>鱼种备注</t>
+          <t>是否允许使用</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>策划备注，UI 可不显示。</t>
+          <t>FALSE：可买但不可装备、不可开船。</t>
         </is>
       </c>
     </row>
@@ -3611,81 +3676,279 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>clueId</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>线索ID</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FALSE 不参与抽选。</t>
+          <t>唯一主键。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>spot_tags</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>clueType</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>线索类型</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>点位所属塘。</t>
+          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>spot_tags</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>spotId</t>
+          <t>clueText</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>钓点ID</t>
+          <t>线索文案</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>与运行时 spotId 对齐。</t>
+          <t>坐席后聊天气泡展示的中文。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>加权随机相对权重，默认 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>minPlayerLevel</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>最低钓鱼等级</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>minPondLevel</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>最低塘熟练度</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>pondCategory</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>塘分级过滤</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>空=全塘；否则仅匹配该分级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>spotTag</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>点位标签过滤</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>空=不限；与 spot_tags.tags 命中任一即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>speciesHint</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>鱼种备注</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>策划备注，UI 可不显示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>FALSE 不参与抽选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>spot_tags</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>鱼塘ID</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>点位所属塘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>spotId</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>钓点ID</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>与运行时 spotId 对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>标签列表</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>逗号分隔，如 weed,shade。</t>
         </is>
@@ -3697,6 +3960,375 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>biteRateMul</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>escapeRateMul</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>infoRevealMul</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>qualityWeightSkew</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sizeCapMul</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pondXpMul</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fineChancePerHour</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fineGold</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>policeWarningMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>鱼塘分级</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>咬钩倍率</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>脱钩倍率</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>信息揭示倍率</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>品质权重倾斜</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>体长上限倍率</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>塘经验倍率</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>每小时出警概率</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>超时罚款金币</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>出警时限毫秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>wilderness</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>forbidden</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3910,7 +4542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4019,7 +4651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4141,7 +4773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4926,7 +5558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5186,7 +5818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5345,7 +5977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6556,7 +7188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8290,6 +8922,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>minQuality</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>minSizeRatio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>maxSizeRatio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>goldMulVsSell</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>playerXp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pondXp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sizeGainMinM</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sizeGainMaxM</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sizeGainMode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>最低品质</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>最小体长比</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>最大体长比</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>回鱼金倍率</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>玩家经验</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>鱼塘经验</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>增重下限m</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>增重上限m</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>增重模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gray</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>uniform_random</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8407,7 +9192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9054,7 +9839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12350,7 +13135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12631,373 +13416,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>biteRateMul</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>escapeRateMul</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>infoRevealMul</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>qualityWeightSkew</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sizeCapMul</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pondXpMul</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fineChancePerHour</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fineGold</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>policeWarningMs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>鱼塘分级</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>咬钩倍率</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>脱钩倍率</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>信息揭示倍率</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>品质权重倾斜</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>体长上限倍率</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>塘经验倍率</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>每小时出警概率</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>超时罚款金币</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>出警时限毫秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>advanced</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>novice</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>veteran</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>wilderness</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>reservoir</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>forbidden</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>800</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>giant</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/钓鱼玩法固定数值表.xlsx
+++ b/钓鱼玩法固定数值表.xlsx
@@ -22,9 +22,11 @@
     <sheet name="pond_fish_size_cap" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="rods" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="baits" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="vessels" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="spot_clue_texts" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="spot_tags" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="groundbaits" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="vessels" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="spot_clue_texts" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="spot_tags" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="achievements" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,6 +500,88 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>窝料ID
+程序主键。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>中文名
+Overlay 显示名。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>解锁钓鱼等级
+低于此等级不可打窝。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>单次金币
+打窝开始时扣除。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>打窝等待毫秒
+groundbaiting phase 时长。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>持续分钟
+与 maxBites 先到失效。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>持续口数
+与 durationMin 先到失效。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>每层咬钩参考
+策划标注；实际用 maxBonus/stackK 曲线。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>咬钩加成渐近上限
+bonus=maxBonus*(1-exp(-stackK*stack))。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>曲线速率
+非线性叠层速率。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>尺寸每层增益m
+临时，不写库。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>尺寸增益总帽m
+临时 sizeBonus 上限。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>策划</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>船具ID
 程序主键。</t>
       </text>
@@ -536,7 +620,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment17.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -606,7 +690,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment18.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>策划</author>
@@ -628,6 +712,70 @@
       <text>
         <t>标签列表
 逗号分隔，如 weed,shade。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment19.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>策划</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>成就ID
+程序主键。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>名称
+展示名。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>描述
+条件说明；隐藏成就未解锁时客户端不剧透。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>图标键
+资源键。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>分类
+catch/social/progress/album。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>条件类型
+catch_count/codex_count/return_count/max_size/album_pins。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>条件阈值
+达标阈值。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>排序
+展示序，小在前。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>隐藏成就
+TRUE：未解锁不展示条件。</t>
       </text>
     </comment>
   </commentList>
@@ -1327,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1405,44 +1553,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ponds</t>
+          <t>_meta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>maxStackCount</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>打窝层数上限</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>程序主键，进塘/扣费/地图都用这个。</t>
+          <t>FEAT-GROUND-01 全局硬 cap，默认 50。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ponds</t>
+          <t>_meta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>biteMulGlobalCap</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>鱼塘名</t>
+          <t>咬钩总倍率软帽</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中文显示名。</t>
+          <t>相对无窝基线的全局 soft cap，建议 1.5。</t>
         </is>
       </c>
     </row>
@@ -1454,17 +1602,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pondCategory</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>鱼塘分级</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>novice/advanced/veteran/wilderness/reservoir/forbidden/giant。</t>
+          <t>程序主键，进塘/扣费/地图都用这个。</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1624,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mapZoneId</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>地图分区</t>
+          <t>鱼塘名</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>世界地图分区 ID。</t>
+          <t>中文显示名。</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1646,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feePer2h</t>
+          <t>pondCategory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>每2小时入场费</t>
+          <t>鱼塘分级</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金币；0 表示不收费。</t>
+          <t>novice/advanced/veteran/wilderness/reservoir/forbidden/giant。</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1668,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>maxFeeChargesPerDay</t>
+          <t>mapZoneId</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>每日扣费次数上限</t>
+          <t>地图分区</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>按 2 小时切片累计。</t>
+          <t>世界地图分区 ID。</t>
         </is>
       </c>
     </row>
@@ -1542,17 +1690,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>unlock</t>
+          <t>feePer2h</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>解锁条件</t>
+          <t>每2小时入场费</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>onboarding / level:N / guide_only。</t>
+          <t>金币；0 表示不收费。</t>
         </is>
       </c>
     </row>
@@ -1564,17 +1712,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>isOpen</t>
+          <t>maxFeeChargesPerDay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>是否开放</t>
+          <t>每日扣费次数上限</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FALSE 的塘不能进（如巨物塘壳）。</t>
+          <t>按 2 小时切片累计。</t>
         </is>
       </c>
     </row>
@@ -1586,17 +1734,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>showOnWorldMap</t>
+          <t>unlock</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>是否上地图</t>
+          <t>解锁条件</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FALSE 则世界地图不画（新手练习塘）。</t>
+          <t>onboarding / level:N / guide_only。</t>
         </is>
       </c>
     </row>
@@ -1608,17 +1756,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>isOpen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>最低钓鱼等级</t>
+          <t>是否开放</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>低于此等级不能进塘。</t>
+          <t>FALSE 的塘不能进（如巨物塘壳）。</t>
         </is>
       </c>
     </row>
@@ -1630,17 +1778,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mapX</t>
+          <t>showOnWorldMap</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>地图X</t>
+          <t>是否上地图</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>世界地图坐标 0~1。</t>
+          <t>FALSE 则世界地图不画（新手练习塘）。</t>
         </is>
       </c>
     </row>
@@ -1652,61 +1800,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mapY</t>
+          <t>minPlayerLevel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>地图Y</t>
+          <t>最低钓鱼等级</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>世界地图坐标 0~1。</t>
+          <t>低于此等级不能进塘。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>player_levels</t>
+          <t>ponds</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>mapX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>钓鱼等级</t>
+          <t>地图X</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1~20。</t>
+          <t>世界地图坐标 0~1。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>player_levels</t>
+          <t>ponds</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>xpToNext</t>
+          <t>mapY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>升到下级所需经验</t>
+          <t>地图Y</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20 级为 0。</t>
+          <t>世界地图坐标 0~1。</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1866,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pondXpPerHour</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每小时鱼塘熟练度</t>
+          <t>钓鱼等级</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>挂机时长折算塘经验的参考。</t>
+          <t>1~20。</t>
         </is>
       </c>
     </row>
@@ -1740,61 +1888,61 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>maxPondLevel</t>
+          <t>xpToNext</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>可达到的最高塘等级</t>
+          <t>升到下级所需经验</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>玩家等级对塘升级的软上限。</t>
+          <t>20 级为 0。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>return_rules</t>
+          <t>player_levels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>minQuality</t>
+          <t>pondXpPerHour</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>最低品质</t>
+          <t>每小时鱼塘熟练度</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>低于此品质不可回鱼；gray=灰及以上。</t>
+          <t>挂机时长折算塘经验的参考。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>return_rules</t>
+          <t>player_levels</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>minSizeRatio</t>
+          <t>maxPondLevel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>最小体长比</t>
+          <t>可达到的最高塘等级</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>相对品质最大体长的下限，如 0.2。</t>
+          <t>玩家等级对塘升级的软上限。</t>
         </is>
       </c>
     </row>
@@ -1806,17 +1954,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>maxSizeRatio</t>
+          <t>minQuality</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>最大体长比</t>
+          <t>最低品质</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
+          <t>低于此品质不可回鱼；gray=灰及以上。</t>
         </is>
       </c>
     </row>
@@ -1828,17 +1976,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>goldMulVsSell</t>
+          <t>minSizeRatio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>回鱼金倍率</t>
+          <t>最小体长比</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>回鱼金 = floor(卖价 × 本倍率)，建议 0.70。</t>
+          <t>相对品质最大体长的下限，如 0.2。</t>
         </is>
       </c>
     </row>
@@ -1850,17 +1998,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>playerXp</t>
+          <t>maxSizeRatio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>玩家经验</t>
+          <t>最大体长比</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>每次回鱼发给玩家的熟练度。</t>
+          <t>相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
         </is>
       </c>
     </row>
@@ -1872,17 +2020,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pondXp</t>
+          <t>goldMulVsSell</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>鱼塘经验</t>
+          <t>回鱼金倍率</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>每次回鱼发给当前塘熟练度。</t>
+          <t>回鱼金 = floor(卖价 × 本倍率)，建议 0.70。</t>
         </is>
       </c>
     </row>
@@ -1894,17 +2042,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sizeGainMinM</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>增重下限m</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>塘内实体增重下限。</t>
+          <t>每次回鱼发给玩家的熟练度。</t>
         </is>
       </c>
     </row>
@@ -1916,17 +2064,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sizeGainMaxM</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>增重上限m</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>塘内实体增重上限。</t>
+          <t>每次回鱼发给当前塘熟练度。</t>
         </is>
       </c>
     </row>
@@ -1938,105 +2086,105 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sizeGainMode</t>
+          <t>sizeGainMinM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>增重模式</t>
+          <t>增重下限m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>uniform_random=区间均匀随机。</t>
+          <t>塘内实体增重下限。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pond_levels</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>sizeGainMaxM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>鱼塘等级</t>
+          <t>增重上限m</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1~10。</t>
+          <t>塘内实体增重上限。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pond_levels</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>xpToNext</t>
+          <t>sizeGainMode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>升到下级所需塘经验</t>
+          <t>增重模式</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10 级为 0。</t>
+          <t>uniform_random=区间均匀随机。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>pond_levels</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>鱼塘等级</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>1~10。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>pond_levels</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>xpToNext</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>升到下级所需塘经验</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>商店/图鉴显示。</t>
+          <t>10 级为 0。</t>
         </is>
       </c>
     </row>
@@ -2048,17 +2196,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>食性</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -2070,17 +2218,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>catchGroup</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>钓组</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
+          <t>商店/图鉴显示。</t>
         </is>
       </c>
     </row>
@@ -2092,17 +2240,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>typicalMinM</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>典型最小体长m</t>
+          <t>食性</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>展示参考，不是硬帽。</t>
+          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
@@ -2114,61 +2262,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>typicalMaxM</t>
+          <t>catchGroup</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>典型最大体长m</t>
+          <t>钓组</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>展示参考，不是硬帽。</t>
+          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>typicalMinM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>典型最小体长m</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>与 fish_species 对齐。</t>
+          <t>展示参考，不是硬帽。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>speciesName</t>
+          <t>typicalMaxM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>典型最大体长m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>便于策划阅读。</t>
+          <t>展示参考，不是硬帽。</t>
         </is>
       </c>
     </row>
@@ -2180,17 +2328,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>gray/green/blue/purple/red/orange/gold。</t>
+          <t>与 fish_species 对齐。</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2350,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>playerXp</t>
+          <t>speciesName</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>玩家经验</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>钓上该品质该种鱼给玩家的经验。</t>
+          <t>便于策划阅读。</t>
         </is>
       </c>
     </row>
@@ -2224,61 +2372,61 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pondXp</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>鱼塘经验</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>同时给当前塘熟练度的经验。</t>
+          <t>gray/green/blue/purple/red/orange/gold。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>卖价品质底表；空行表示下面是钓组系数。</t>
+          <t>钓上该品质该种鱼给玩家的经验。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fish_sell</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>QUALITY_BASE</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>品质底价</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>卖价公式底数。</t>
+          <t>同时给当前塘熟练度的经验。</t>
         </is>
       </c>
     </row>
@@ -2290,17 +2438,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SIZE_REF</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>体长参考m</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>卖价公式尺寸归一化。</t>
+          <t>卖价品质底表；空行表示下面是钓组系数。</t>
         </is>
       </c>
     </row>
@@ -2312,17 +2460,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MIN_SELL</t>
+          <t>QUALITY_BASE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>最低卖价</t>
+          <t>品质底价</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>向下取整后的保底。</t>
+          <t>卖价公式底数。</t>
         </is>
       </c>
     </row>
@@ -2334,17 +2482,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>catchGroup</t>
+          <t>SIZE_REF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>钓组</t>
+          <t>体长参考m</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SPECIES_MULT 所对应的钓组。</t>
+          <t>卖价公式尺寸归一化。</t>
         </is>
       </c>
     </row>
@@ -2356,61 +2504,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SPECIES_MULT</t>
+          <t>MIN_SELL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>钓组卖价系数</t>
+          <t>最低卖价</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>乘在品质底价上。</t>
+          <t>向下取整后的保底。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>catchGroup</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>鱼塘分级</t>
+          <t>钓组</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>与 ponds.pondCategory 对应。</t>
+          <t>SPECIES_MULT 所对应的钓组。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_sell</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>biteRateMul</t>
+          <t>SPECIES_MULT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>咬钩倍率</t>
+          <t>钓组卖价系数</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>塘级对咬钩率的乘区。</t>
+          <t>乘在品质底价上。</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2570,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>escapeRateMul</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>脱钩倍率</t>
+          <t>鱼塘分级</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>塘级对脱钩率的乘区。</t>
+          <t>与 ponds.pondCategory 对应。</t>
         </is>
       </c>
     </row>
@@ -2444,17 +2592,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>infoRevealMul</t>
+          <t>biteRateMul</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>信息揭示倍率</t>
+          <t>咬钩倍率</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>线索/信息量。</t>
+          <t>塘级对咬钩率的乘区。</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2614,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qualityWeightSkew</t>
+          <t>escapeRateMul</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>品质权重倾斜</t>
+          <t>脱钩倍率</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>&gt;1 偏向高品质。</t>
+          <t>塘级对脱钩率的乘区。</t>
         </is>
       </c>
     </row>
@@ -2488,17 +2636,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>sizeCapMul</t>
+          <t>infoRevealMul</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>体长上限倍率</t>
+          <t>信息揭示倍率</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>乘在鱼种尺寸帽上。</t>
+          <t>线索/信息量。</t>
         </is>
       </c>
     </row>
@@ -2510,17 +2658,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pondXpMul</t>
+          <t>qualityWeightSkew</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>塘经验倍率</t>
+          <t>品质权重倾斜</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>该分级塘熟练度获取。</t>
+          <t>&gt;1 偏向高品质。</t>
         </is>
       </c>
     </row>
@@ -2532,17 +2680,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fineChancePerHour</t>
+          <t>sizeCapMul</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>每小时出警概率</t>
+          <t>体长上限倍率</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
+          <t>乘在鱼种尺寸帽上。</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2702,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>fineGold</t>
+          <t>pondXpMul</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>超时罚款金币</t>
+          <t>塘经验倍率</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
+          <t>该分级塘熟练度获取。</t>
         </is>
       </c>
     </row>
@@ -2576,61 +2724,61 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>policeWarningMs</t>
+          <t>fineChancePerHour</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>出警时限毫秒</t>
+          <t>每小时出警概率</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
+          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>fineGold</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>超时罚款金币</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>该塘可出的鱼。</t>
+          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>policeWarningMs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>出警时限毫秒</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>库存模板条目。</t>
+          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
         </is>
       </c>
     </row>
@@ -2642,17 +2790,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>common 常驻 / rare 稀有。</t>
+          <t>该塘可出的鱼。</t>
         </is>
       </c>
     </row>
@@ -2664,17 +2812,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spawnWeight</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>刷新权重</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>相对权重。</t>
+          <t>库存模板条目。</t>
         </is>
       </c>
     </row>
@@ -2686,61 +2834,61 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FALSE 则该条不参与刷新。</t>
+          <t>common 常驻 / rare 稀有。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>spawnWeight</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>刷新权重</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>品质软帽。</t>
+          <t>相对权重。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pond_quality_cap</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>minQuality</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>最低品质</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>该塘随机品质下限。</t>
+          <t>FALSE 则该条不参与刷新。</t>
         </is>
       </c>
     </row>
@@ -2752,17 +2900,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>maxQuality</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>最高品质</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>该塘随机品质上限。</t>
+          <t>品质软帽。</t>
         </is>
       </c>
     </row>
@@ -2774,61 +2922,61 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>minQuality</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>最低品质</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>策划说明，不进规则。</t>
+          <t>该塘随机品质下限。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>maxQuality</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>最高品质</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>体长硬帽。</t>
+          <t>该塘随机品质上限。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>pond_fish_size_cap</t>
+          <t>pond_quality_cap</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>该塘该种鱼。</t>
+          <t>策划说明，不进规则。</t>
         </is>
       </c>
     </row>
@@ -2840,17 +2988,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>按品质分档的尺寸帽。</t>
+          <t>体长硬帽。</t>
         </is>
       </c>
     </row>
@@ -2862,17 +3010,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>minSizeM</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>最小体长m</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>随机体长下限。</t>
+          <t>该塘该种鱼。</t>
         </is>
       </c>
     </row>
@@ -2884,61 +3032,61 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>maxSizeM</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>最大体长m</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>随机体长上限。</t>
+          <t>按品质分档的尺寸帽。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>rodId</t>
+          <t>minSizeM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>钓竿ID</t>
+          <t>最小体长m</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>程序主键，商店与装备用。</t>
+          <t>随机体长下限。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_fish_size_cap</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>maxSizeM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>最大体长m</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>随机体长上限。</t>
         </is>
       </c>
     </row>
@@ -2950,17 +3098,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>subType</t>
+          <t>rodId</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>竿型</t>
+          <t>钓竿ID</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
+          <t>程序主键，商店与装备用。</t>
         </is>
       </c>
     </row>
@@ -2972,17 +3120,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0 表示新手赠送，商店不可回购。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -2994,17 +3142,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>biteBonus</t>
+          <t>subType</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>咬钩加成</t>
+          <t>竿型</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
+          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
         </is>
       </c>
     </row>
@@ -3016,17 +3164,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>escapeReduction</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>防脱</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
+          <t>0 表示新手赠送，商店不可回购。</t>
         </is>
       </c>
     </row>
@@ -3038,17 +3186,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>breakSizeM</t>
+          <t>biteBonus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>超规格体长m</t>
+          <t>咬钩加成</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>成功钓上大于该体长的鱼计入超规格。</t>
+          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
         </is>
       </c>
     </row>
@@ -3060,17 +3208,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>breakMaxLandings</t>
+          <t>escapeReduction</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>超规格成功上限</t>
+          <t>防脱</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
+          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
         </is>
       </c>
     </row>
@@ -3082,17 +3230,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fitGray</t>
+          <t>breakSizeM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>灰品质适配</t>
+          <t>超规格体长m</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
+          <t>成功钓上大于该体长的鱼计入超规格。</t>
         </is>
       </c>
     </row>
@@ -3104,17 +3252,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fitGreen</t>
+          <t>breakMaxLandings</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>绿品质适配</t>
+          <t>超规格成功上限</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3274,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fitBlue</t>
+          <t>fitGray</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>蓝品质适配</t>
+          <t>灰品质适配</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3296,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fitPurple</t>
+          <t>fitGreen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>紫品质适配</t>
+          <t>绿品质适配</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3170,12 +3318,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fitRed</t>
+          <t>fitBlue</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>红品质适配</t>
+          <t>蓝品质适配</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3192,12 +3340,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fitOrange</t>
+          <t>fitPurple</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>橙品质适配</t>
+          <t>紫品质适配</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3214,12 +3362,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fitGold</t>
+          <t>fitRed</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>金品质适配</t>
+          <t>红品质适配</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3236,17 +3384,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fitStillBait</t>
+          <t>fitOrange</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>静水底钓适配</t>
+          <t>橙品质适配</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>对应 catchGroup=still_bait。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
@@ -3258,17 +3406,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fitStreamLight</t>
+          <t>fitGold</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>溪流轻口适配</t>
+          <t>金品质适配</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>对应 catchGroup=stream_light。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
@@ -3280,17 +3428,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fitLurePredator</t>
+          <t>fitStillBait</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>路亚掠食适配</t>
+          <t>静水底钓适配</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>对应 catchGroup=lure_predator。</t>
+          <t>对应 catchGroup=still_bait。</t>
         </is>
       </c>
     </row>
@@ -3302,17 +3450,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fitCastHeavy</t>
+          <t>fitStreamLight</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>重抛适配</t>
+          <t>溪流轻口适配</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>对应 catchGroup=cast_heavy。</t>
+          <t>对应 catchGroup=stream_light。</t>
         </is>
       </c>
     </row>
@@ -3324,61 +3472,61 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fitGiantGame</t>
+          <t>fitLurePredator</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>巨物适配</t>
+          <t>路亚掠食适配</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>对应 catchGroup=giant_game。</t>
+          <t>对应 catchGroup=lure_predator。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>baitId</t>
+          <t>fitCastHeavy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>鱼饵ID</t>
+          <t>重抛适配</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>对应 catchGroup=cast_heavy。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>fitGiantGame</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>巨物适配</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>对应 catchGroup=giant_game。</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3538,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>baitId</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>对口食性</t>
+          <t>鱼饵ID</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -3412,17 +3560,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0 表示开局可用。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -3434,17 +3582,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>costGoldPerUse</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>每次扣金</t>
+          <t>对口食性</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
+          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3604,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>biteBonusHerbivore</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>对草食咬钩加成</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>0 表示开局可用。</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3626,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>biteBonusOmnivore</t>
+          <t>costGoldPerUse</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>对杂食咬钩加成</t>
+          <t>每次扣金</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
         </is>
       </c>
     </row>
@@ -3500,17 +3648,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>biteBonusCarnivore</t>
+          <t>biteBonusHerbivore</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>对肉食咬钩加成</t>
+          <t>对草食咬钩加成</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>如 0.07 = +7%。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
@@ -3522,435 +3670,941 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>isDefaultInfinite</t>
+          <t>biteBonusOmnivore</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>是否无限基础饵</t>
+          <t>对杂食咬钩加成</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TRUE 的饵永不短缺，也不扣金。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>vesselId</t>
+          <t>biteBonusCarnivore</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>船具ID</t>
+          <t>对肉食咬钩加成</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>如 0.07 = +7%。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isDefaultInfinite</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>是否无限基础饵</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>TRUE 的饵永不短缺，也不扣金。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>groundbaitId</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>窝料ID</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>低于此等级不能买。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>一次性购入。</t>
+          <t>Overlay 显示名。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>placeholderCatchCount</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>占位捕捞次数</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>表内预留，当前不生效。</t>
+          <t>低于此等级不可打窝。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>enabledUse</t>
+          <t>costGoldPerUse</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>是否允许使用</t>
+          <t>单次金币</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>FALSE：可买但不可装备、不可开船。</t>
+          <t>打窝开始时扣除。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>clueId</t>
+          <t>castDurationMs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>线索ID</t>
+          <t>打窝等待毫秒</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>唯一主键。</t>
+          <t>groundbaiting phase 时长。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>clueType</t>
+          <t>durationMin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>线索类型</t>
+          <t>持续分钟</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
+          <t>与 maxBites 先到失效。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>clueText</t>
+          <t>maxBites</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>线索文案</t>
+          <t>持续口数</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>坐席后聊天气泡展示的中文。</t>
+          <t>与 durationMin 先到失效。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>perStackBiteBonus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>每层咬钩参考</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>加权随机相对权重，默认 1。</t>
+          <t>策划标注；实际用 maxBonus/stackK 曲线。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>maxBonus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>最低钓鱼等级</t>
+          <t>咬钩加成渐近上限</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>bonus=maxBonus*(1-exp(-stackK*stack))。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>minPondLevel</t>
+          <t>stackK</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>最低塘熟练度</t>
+          <t>曲线速率</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>非线性叠层速率。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>pondCategory</t>
+          <t>sizeBonusPerStack</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>塘分级过滤</t>
+          <t>尺寸每层增益m</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>空=全塘；否则仅匹配该分级。</t>
+          <t>临时，不写库。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>spotTag</t>
+          <t>maxSizeBonus</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>点位标签过滤</t>
+          <t>尺寸增益总帽m</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>空=不限；与 spot_tags.tags 命中任一即可。</t>
+          <t>临时 sizeBonus 上限。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>speciesHint</t>
+          <t>vesselId</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>鱼种备注</t>
+          <t>船具ID</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>策划备注，UI 可不显示。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>FALSE 不参与抽选。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>spot_tags</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>点位所属塘。</t>
+          <t>低于此等级不能买。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>spot_tags</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>spotId</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>钓点ID</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>与运行时 spotId 对齐。</t>
+          <t>一次性购入。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>vessels</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>placeholderCatchCount</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>占位捕捞次数</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>表内预留，当前不生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>vessels</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>enabledUse</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>是否允许使用</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>FALSE：可买但不可装备、不可开船。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>clueId</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>线索ID</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>唯一主键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>clueType</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>线索类型</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>clueText</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>线索文案</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>坐席后聊天气泡展示的中文。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>加权随机相对权重，默认 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>minPlayerLevel</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>最低钓鱼等级</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>minPondLevel</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>最低塘熟练度</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>未达到不进入抽选池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pondCategory</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>塘分级过滤</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>空=全塘；否则仅匹配该分级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>spotTag</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>点位标签过滤</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>空=不限；与 spot_tags.tags 命中任一即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>speciesHint</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>鱼种备注</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>策划备注，UI 可不显示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>spot_clue_texts</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>FALSE 不参与抽选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>spot_tags</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>鱼塘ID</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>点位所属塘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>spotId</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>钓点ID</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>与运行时 spotId 对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>spot_tags</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>标签列表</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>逗号分隔，如 weed,shade。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>achievementId</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>成就ID</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>程序主键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>展示名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>条件说明；隐藏成就未解锁时客户端不剧透。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>iconKey</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>图标键</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>资源键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>catch/social/progress/album。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>conditionType</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>条件类型</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>catch_count/codex_count/return_count/max_size/album_pins。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>conditionValue</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>条件阈值</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>达标阈值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>sortOrder</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>展示序，小在前。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>isHidden</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>隐藏成就</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TRUE：未解锁不展示条件。</t>
         </is>
       </c>
     </row>
@@ -5824,6 +6478,285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>groundbaitId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unlockPlayerLevel</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>costGoldPerUse</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>castDurationMs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>durationMin</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>maxBites</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>perStackBiteBonus</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>maxBonus</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>stackK</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>sizeBonusPerStack</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>maxSizeBonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>窝料ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>解锁钓鱼等级</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>单次金币</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>打窝等待毫秒</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>持续分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>持续口数</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>每层咬钩参考</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>咬钩加成渐近上限</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>曲线速率</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>尺寸每层增益m</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>尺寸增益总帽m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gb-basic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>基础窝料</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gb-mix</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>混合窝料</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gb-premium</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>精品窝料</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5977,7 +6910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7188,7 +8121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7333,11 +8266,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7399,13 +8332,409 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>maxStackCount</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>biteMulGlobalCap</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>albumPinCap</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>schemaNote</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FEAT-PROG-01+RETURN-01+GROUND-01+ALBUM-01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>achievementId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iconKey</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>conditionType</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>conditionValue</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sortOrder</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>isHidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>成就ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>图标键</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>条件类型</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>条件阈值</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>隐藏成就</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ach-first-catch</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>初出茅庐</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>首次将鱼收入背包</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ach_first_catch</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>catch</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>catch_count</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ach-codex-5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>图鉴新芽</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>图鉴解锁达到 5 种</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ach_codex_5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>codex_count</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ach-codex-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>博物渔者</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>图鉴解锁达到 20 种</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ach_codex_20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>codex_count</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ach-return-1</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEAT-PROG-01</t>
-        </is>
+          <t>放生有情</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>成功回鱼至少 1 次</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ach_return_1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>catch</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>return_count</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ach-big-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>大鱼临门</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>单次捕获尺寸达到 0.8m</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ach_big_08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>catch</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>max_size</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ach-album-3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>相册收藏家</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>相册精选钉选达到 3 张</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ach_album_3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>album</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>album_pins</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/钓鱼玩法固定数值表.xlsx
+++ b/钓鱼玩法固定数值表.xlsx
@@ -199,11 +199,17 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
+        <t>塘类型中文名
+新手/高级/老手/野外/水库/禁止/巨物。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
         <t>品质
 gray…gold。</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>品质权重
 选好种后按此表加权抽品质。</t>
@@ -990,67 +996,73 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>最低品质
-低于此品质不可回鱼；gray=灰及以上。</t>
+回鱼最低品质（默认 purple）。</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>最小体长比
-相对品质最大体长的下限，如 0.2。</t>
+        <t>自动最低品质
+与 minQuality 对齐；自动回鱼门槛。</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>最大体长比
-相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
+        <t>最低体重斤
+市斤体重 ≥ 本值才可回鱼（默认 10）。</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>回鱼金倍率
-回鱼金 = floor(卖价 × 本倍率)，建议 1.50。</t>
+        <t>超重档斤
+市斤体重 &gt; 本值时按 goldMulHeavy（默认 100）。</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>最大体长比
+兼容字段；准入已改体重/品质。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>回鱼金倍率
+体重 ≥minWeightJin 且 ≤heavyWeightJin：floor(卖价×本倍率)，默认 1.50。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>超重回鱼倍率
+体重 &gt;heavyWeightJin：floor(卖价×本倍率)，默认 3.00。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>玩家经验
 每次回鱼发给玩家的熟练度。</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>鱼塘经验
 每次回鱼发给当前塘熟练度。</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>增重下限m
 塘内实体增重下限。</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>增重上限m
 塘内实体增重上限。</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>增重模式
 uniform_random=区间均匀随机。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>自动回鱼最低品质
-FEAT-RETURN-02 如 purple。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>自动回鱼最低体长比
-相对品质 max，如 0.75。</t>
       </text>
     </comment>
   </commentList>
@@ -1588,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2275,7 +2287,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>低于此品质不可回鱼；gray=灰及以上。</t>
+          <t>回鱼最低品质（默认 purple）。</t>
         </is>
       </c>
     </row>
@@ -2287,17 +2299,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>minSizeRatio</t>
+          <t>autoMinQuality</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>最小体长比</t>
+          <t>自动最低品质</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>相对品质最大体长的下限，如 0.2。</t>
+          <t>与 minQuality 对齐；自动回鱼门槛。</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2321,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>maxSizeRatio</t>
+          <t>minWeightJin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>最大体长比</t>
+          <t>最低体重斤</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>相对品质最大体长的上限；1.0 表示满尺寸不可回。</t>
+          <t>市斤体重 ≥ 本值才可回鱼（默认 10）。</t>
         </is>
       </c>
     </row>
@@ -2331,17 +2343,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>goldMulVsSell</t>
+          <t>heavyWeightJin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>回鱼金倍率</t>
+          <t>超重档斤</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>回鱼金 = floor(卖价 × 本倍率)，建议 1.50。</t>
+          <t>市斤体重 &gt; 本值时按 goldMulHeavy（默认 100）。</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2365,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>playerXp</t>
+          <t>maxSizeRatio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>玩家经验</t>
+          <t>最大体长比</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>每次回鱼发给玩家的熟练度。</t>
+          <t>兼容字段；准入已改体重/品质。</t>
         </is>
       </c>
     </row>
@@ -2375,17 +2387,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pondXp</t>
+          <t>goldMulVsSell</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>鱼塘经验</t>
+          <t>回鱼金倍率</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>每次回鱼发给当前塘熟练度。</t>
+          <t>体重 ≥minWeightJin 且 ≤heavyWeightJin：floor(卖价×本倍率)，默认 1.50。</t>
         </is>
       </c>
     </row>
@@ -2397,17 +2409,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sizeGainMinM</t>
+          <t>goldMulHeavy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>增重下限m</t>
+          <t>超重回鱼倍率</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>塘内实体增重下限。</t>
+          <t>体重 &gt;heavyWeightJin：floor(卖价×本倍率)，默认 3.00。</t>
         </is>
       </c>
     </row>
@@ -2419,17 +2431,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sizeGainMaxM</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>增重上限m</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>塘内实体增重上限。</t>
+          <t>每次回鱼发给玩家的熟练度。</t>
         </is>
       </c>
     </row>
@@ -2441,17 +2453,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sizeGainMode</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>增重模式</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>uniform_random=区间均匀随机。</t>
+          <t>每次回鱼发给当前塘熟练度。</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2475,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>autoMinQuality</t>
+          <t>sizeGainMinM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>自动回鱼最低品质</t>
+          <t>增重下限m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FEAT-RETURN-02 如 purple。</t>
+          <t>塘内实体增重下限。</t>
         </is>
       </c>
     </row>
@@ -2485,39 +2497,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>autoMinSizeRatio</t>
+          <t>sizeGainMaxM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>自动回鱼最低体长比</t>
+          <t>增重上限m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>相对品质 max，如 0.75。</t>
+          <t>塘内实体增重上限。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pond_levels</t>
+          <t>return_rules</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>sizeGainMode</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>鱼塘等级</t>
+          <t>增重模式</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1~10。</t>
+          <t>uniform_random=区间均匀随机。</t>
         </is>
       </c>
     </row>
@@ -2529,39 +2541,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>xpToNext</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>升到下级所需塘经验</t>
+          <t>鱼塘等级</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10 级为 0。</t>
+          <t>1~10。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fish_species</t>
+          <t>pond_levels</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>xpToNext</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>升到下级所需塘经验</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>10 级为 0。</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2585,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>商店/图鉴显示。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -2595,17 +2607,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>食性</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>商店/图鉴显示。</t>
         </is>
       </c>
     </row>
@@ -2617,17 +2629,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>catchGroup</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>钓组</t>
+          <t>食性</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
+          <t>herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
@@ -2639,17 +2651,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>typicalMinM</t>
+          <t>catchGroup</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>典型最小体长m</t>
+          <t>钓组</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>图鉴展示参考，不参与体长结算。</t>
+          <t>still_bait 静水底钓 / stream_light 溪流轻口 / lure_predator 路亚掠食 / cast_heavy 重抛 / giant_game 巨物。</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2673,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>typicalMaxM</t>
+          <t>typicalMinM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>典型最大体长m</t>
+          <t>典型最小体长m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2683,17 +2695,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>rarityTier</t>
+          <t>typicalMaxM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>稀有度档</t>
+          <t>典型最大体长m</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>common/uncommon/rare/legendary；决定 qualityMax。</t>
+          <t>图鉴展示参考，不参与体长结算。</t>
         </is>
       </c>
     </row>
@@ -2705,17 +2717,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nationwide</t>
+          <t>rarityTier</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>全国广布</t>
+          <t>稀有度档</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TRUE 则所有 bioRegion 可出。</t>
+          <t>common/uncommon/rare/legendary；决定 qualityMax。</t>
         </is>
       </c>
     </row>
@@ -2727,17 +2739,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qualityMin</t>
+          <t>nationwide</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>品质下限序</t>
+          <t>全国广布</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>恒为 1（gray）；播种品质带下限。</t>
+          <t>TRUE 则所有 bioRegion 可出。</t>
         </is>
       </c>
     </row>
@@ -2749,39 +2761,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>qualityMax</t>
+          <t>qualityMin</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>品质上限序</t>
+          <t>品质下限序</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1=gray…7=gold；稀有度抬高上限，与塘权重求交。</t>
+          <t>恒为 1（gray）；播种品质带下限。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pond_fish_pool</t>
+          <t>fish_species</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>qualityMax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>品质上限序</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>该塘可出的鱼（仅种，不含品质）。</t>
+          <t>1=gray…7=gold；稀有度抬高上限，与塘权重求交。</t>
         </is>
       </c>
     </row>
@@ -2793,17 +2805,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>种池条目。</t>
+          <t>该塘可出的鱼（仅种，不含品质）。</t>
         </is>
       </c>
     </row>
@@ -2815,17 +2827,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>speciesName</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>只读展示，与 fish_species.name 一致。</t>
+          <t>种池条目。</t>
         </is>
       </c>
     </row>
@@ -2837,17 +2849,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spawnWeight</t>
+          <t>speciesName</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>种刷新权重</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>抽种相对权重；品质另走 pond_category_quality_weights。</t>
+          <t>只读展示，与 fish_species.name 一致。</t>
         </is>
       </c>
     </row>
@@ -2859,39 +2871,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>spawnWeight</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>种刷新权重</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FALSE 则该种不参与刷新。</t>
+          <t>抽种相对权重；品质另走 pond_category_quality_weights。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>pond_category_quality_weights</t>
+          <t>pond_fish_pool</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pondCategory</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>塘分级</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>novice…giant；播种/补充抽品质用。</t>
+          <t>FALSE 则该种不参与刷新。</t>
         </is>
       </c>
     </row>
@@ -2903,17 +2915,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>pondCategory</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>塘分级</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>gray…gold。</t>
+          <t>novice…giant；播种/补充抽品质用。</t>
         </is>
       </c>
     </row>
@@ -2925,24 +2937,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spawnWeight</t>
+          <t>pondCategoryName</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>品质权重</t>
+          <t>塘类型中文名</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>选好种后按此表加权抽品质。</t>
+          <t>新手/高级/老手/野外/水库/禁止/巨物。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fish_quality_stats</t>
+          <t>pond_category_quality_weights</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2957,29 +2969,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>gray…gold；玩法+卖价同表。</t>
+          <t>gray…gold。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fish_quality_stats</t>
+          <t>pond_category_quality_weights</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sizeCapM</t>
+          <t>spawnWeight</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>尺寸上限m</t>
+          <t>品质权重</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>品质体长硬帽。</t>
+          <t>选好种后按此表加权抽品质。</t>
         </is>
       </c>
     </row>
@@ -2991,17 +3003,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>biteBaseAtMaxSize</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>满尺寸咬钩基数</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>公式读表。</t>
+          <t>gray…gold；玩法+卖价同表。</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3025,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>displayName</t>
+          <t>sizeCapM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>尺寸上限m</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中文品质名。</t>
+          <t>品质体长硬帽。</t>
         </is>
       </c>
     </row>
@@ -3035,17 +3047,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QUALITY_BASE</t>
+          <t>biteBaseAtMaxSize</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>品质底价</t>
+          <t>满尺寸咬钩基数</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>卖价公式底数；钓组不参与卖价。</t>
+          <t>公式读表。</t>
         </is>
       </c>
     </row>
@@ -3057,17 +3069,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SIZE_REF</t>
+          <t>displayName</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>体长参考m</t>
+          <t>显示名</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>卖价公式尺寸归一化。</t>
+          <t>中文品质名。</t>
         </is>
       </c>
     </row>
@@ -3079,61 +3091,61 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MIN_SELL</t>
+          <t>QUALITY_BASE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>最低卖价</t>
+          <t>品质底价</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>向下取整后的保底。</t>
+          <t>卖价公式底数；钓组不参与卖价。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fishing_formula_constants</t>
+          <t>fish_quality_stats</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>SIZE_REF</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>常数键</t>
+          <t>体长参考m</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>fishing.ts 公式常数名。</t>
+          <t>卖价公式尺寸归一化。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fishing_formula_constants</t>
+          <t>fish_quality_stats</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>MIN_SELL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>最低卖价</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>数值。</t>
+          <t>向下取整后的保底。</t>
         </is>
       </c>
     </row>
@@ -3145,61 +3157,61 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>key</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>常数键</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>该常数用途注释。</t>
+          <t>fishing.ts 公式常数名。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fishing_formula_constants</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>speciesId</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>鱼种ID</t>
+          <t>值</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>与 fish_species 对齐。</t>
+          <t>数值。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fish_xp</t>
+          <t>fishing_formula_constants</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>speciesName</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>便于策划阅读。</t>
+          <t>该常数用途注释。</t>
         </is>
       </c>
     </row>
@@ -3211,17 +3223,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>speciesId</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>鱼种ID</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>gray/green/blue/purple/red/orange/gold。</t>
+          <t>与 fish_species 对齐。</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3245,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>playerXp</t>
+          <t>speciesName</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>玩家经验</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>钓上该品质该种鱼给玩家的经验。</t>
+          <t>便于策划阅读。</t>
         </is>
       </c>
     </row>
@@ -3255,61 +3267,61 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>pondXp</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>鱼塘经验</t>
+          <t>品质</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>同时给当前塘熟练度的经验。</t>
+          <t>gray/green/blue/purple/red/orange/gold。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>playerXp</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>鱼塘分级</t>
+          <t>玩家经验</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>与 ponds.pondCategory 对应。</t>
+          <t>钓上该品质该种鱼给玩家的经验。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>pond_modifiers</t>
+          <t>fish_xp</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>biteRateMul</t>
+          <t>pondXp</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>咬钩倍率</t>
+          <t>鱼塘经验</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>塘级对咬钩率的乘区。</t>
+          <t>同时给当前塘熟练度的经验。</t>
         </is>
       </c>
     </row>
@@ -3321,17 +3333,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>escapeRateMul</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>脱钩倍率</t>
+          <t>鱼塘分级</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>塘级对脱钩率的乘区。</t>
+          <t>与 ponds.pondCategory 对应。</t>
         </is>
       </c>
     </row>
@@ -3343,17 +3355,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>infoRevealMul</t>
+          <t>biteRateMul</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>信息揭示倍率</t>
+          <t>咬钩倍率</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>线索/信息量。</t>
+          <t>塘级对咬钩率的乘区。</t>
         </is>
       </c>
     </row>
@@ -3365,17 +3377,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>qualityWeightSkew</t>
+          <t>escapeRateMul</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>品质权重倾斜</t>
+          <t>脱钩倍率</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>&gt;1 偏向高品质。</t>
+          <t>塘级对脱钩率的乘区。</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3399,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sizeCapMul</t>
+          <t>infoRevealMul</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>体长上限倍率</t>
+          <t>信息揭示倍率</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>乘在鱼种尺寸帽上。</t>
+          <t>线索/信息量。</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3421,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>pondXpMul</t>
+          <t>qualityWeightSkew</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>塘经验倍率</t>
+          <t>品质权重倾斜</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>该分级塘熟练度获取。</t>
+          <t>&gt;1 偏向高品质。</t>
         </is>
       </c>
     </row>
@@ -3431,17 +3443,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fineChancePerHour</t>
+          <t>sizeCapMul</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>每小时出警概率</t>
+          <t>体长上限倍率</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
+          <t>乘在鱼种尺寸帽上。</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3465,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fineGold</t>
+          <t>pondXpMul</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>超时罚款金币</t>
+          <t>塘经验倍率</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
+          <t>该分级塘熟练度获取。</t>
         </is>
       </c>
     </row>
@@ -3475,61 +3487,61 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>policeWarningMs</t>
+          <t>fineChancePerHour</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>出警时限毫秒</t>
+          <t>每小时出警概率</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
+          <t>仅 forbidden 使用，初值 0.15。其它分级填 0。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>rodId</t>
+          <t>fineGold</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>钓竿ID</t>
+          <t>超时罚款金币</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>程序主键，商店与装备用。</t>
+          <t>不足则归零。仅 forbidden 使用，初值 800。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>pond_modifiers</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>policeWarningMs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>出警时限毫秒</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>时限内离塘免罚。仅 forbidden 使用，初值 10000。</t>
         </is>
       </c>
     </row>
@@ -3541,17 +3553,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>subType</t>
+          <t>rodId</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>竿型</t>
+          <t>钓竿ID</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
+          <t>程序主键，商店与装备用。</t>
         </is>
       </c>
     </row>
@@ -3563,17 +3575,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0 表示新手赠送，商店不可回购。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3597,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>biteBonus</t>
+          <t>subType</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>咬钩加成</t>
+          <t>竿型</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
+          <t>手竿入门/台钓/溪流/矶钓/路亚/海竿/重路亚/巨物。</t>
         </is>
       </c>
     </row>
@@ -3607,17 +3619,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>escapeReduction</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>防脱</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
+          <t>0 表示新手赠送，商店不可回购。</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3641,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>breakSizeM</t>
+          <t>biteBonus</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>超规格体长m</t>
+          <t>咬钩加成</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>成功钓上大于该体长的鱼计入超规格。</t>
+          <t>加在咬钩判定上的弱加成，如 0.03 = +3%。</t>
         </is>
       </c>
     </row>
@@ -3651,17 +3663,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>breakMaxLandings</t>
+          <t>escapeReduction</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>超规格成功上限</t>
+          <t>防脱</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
+          <t>降低脱钩率的弱减免，如 0.04 = -4%。</t>
         </is>
       </c>
     </row>
@@ -3673,17 +3685,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fitGray</t>
+          <t>breakSizeM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>灰品质适配</t>
+          <t>超规格体长m</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
+          <t>成功钓上大于该体长的鱼计入超规格。</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3707,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fitGreen</t>
+          <t>breakMaxLandings</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>绿品质适配</t>
+          <t>超规格成功上限</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>累计满 N 次后当前装备竿销毁，不能修理。</t>
         </is>
       </c>
     </row>
@@ -3717,17 +3729,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fitBlue</t>
+          <t>fitGray</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>蓝品质适配</t>
+          <t>灰品质适配</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>乘区。</t>
+          <t>乘区；&gt;1 更合适，&lt;1 不合适。</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3751,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fitPurple</t>
+          <t>fitGreen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>紫品质适配</t>
+          <t>绿品质适配</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3761,12 +3773,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fitRed</t>
+          <t>fitBlue</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>红品质适配</t>
+          <t>蓝品质适配</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3783,12 +3795,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fitOrange</t>
+          <t>fitPurple</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>橙品质适配</t>
+          <t>紫品质适配</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3805,12 +3817,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fitGold</t>
+          <t>fitRed</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>金品质适配</t>
+          <t>红品质适配</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3827,17 +3839,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fitStillBait</t>
+          <t>fitOrange</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>静水底钓适配</t>
+          <t>橙品质适配</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>对应 catchGroup=still_bait。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3861,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>fitStreamLight</t>
+          <t>fitGold</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>溪流轻口适配</t>
+          <t>金品质适配</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>对应 catchGroup=stream_light。</t>
+          <t>乘区。</t>
         </is>
       </c>
     </row>
@@ -3871,17 +3883,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>fitLurePredator</t>
+          <t>fitStillBait</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>路亚掠食适配</t>
+          <t>静水底钓适配</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>对应 catchGroup=lure_predator。</t>
+          <t>对应 catchGroup=still_bait。</t>
         </is>
       </c>
     </row>
@@ -3893,17 +3905,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>fitCastHeavy</t>
+          <t>fitStreamLight</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>重抛适配</t>
+          <t>溪流轻口适配</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>对应 catchGroup=cast_heavy。</t>
+          <t>对应 catchGroup=stream_light。</t>
         </is>
       </c>
     </row>
@@ -3915,61 +3927,61 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>fitGiantGame</t>
+          <t>fitLurePredator</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>巨物适配</t>
+          <t>路亚掠食适配</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>对应 catchGroup=giant_game。</t>
+          <t>对应 catchGroup=lure_predator。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>baitId</t>
+          <t>fitCastHeavy</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>鱼饵ID</t>
+          <t>重抛适配</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>对应 catchGroup=cast_heavy。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>baits</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>fitGiantGame</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>巨物适配</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>对应 catchGroup=giant_game。</t>
         </is>
       </c>
     </row>
@@ -3981,17 +3993,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>baitId</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>对口食性</t>
+          <t>鱼饵ID</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4015,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0 表示开局可用。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -4025,17 +4037,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>costGoldPerUse</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>每次扣金</t>
+          <t>对口食性</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
+          <t>any 通用 / herbivore 草食 / omnivore 杂食 / carnivore 肉食。</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4059,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>biteBonusHerbivore</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>对草食咬钩加成</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>0 表示开局可用。</t>
         </is>
       </c>
     </row>
@@ -4069,17 +4081,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>biteBonusOmnivore</t>
+          <t>costGoldPerUse</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>对杂食咬钩加成</t>
+          <t>每次扣金</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>如 0.06 = +6%。</t>
+          <t>咬钩成功时扣除；0 表示不扣金。不进货、无库存。</t>
         </is>
       </c>
     </row>
@@ -4091,17 +4103,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>biteBonusCarnivore</t>
+          <t>biteBonusHerbivore</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>对肉食咬钩加成</t>
+          <t>对草食咬钩加成</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>如 0.07 = +7%。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
@@ -4113,61 +4125,61 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>isDefaultInfinite</t>
+          <t>biteBonusOmnivore</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>是否无限基础饵</t>
+          <t>对杂食咬钩加成</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TRUE 的饵永不短缺，也不扣金。</t>
+          <t>如 0.06 = +6%。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>groundbaits</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>groundbaitId</t>
+          <t>biteBonusCarnivore</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>窝料ID</t>
+          <t>对肉食咬钩加成</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>如 0.07 = +7%。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>groundbaits</t>
+          <t>baits</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isDefaultInfinite</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>是否无限基础饵</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Overlay 显示名。</t>
+          <t>TRUE 的饵永不短缺，也不扣金。</t>
         </is>
       </c>
     </row>
@@ -4179,17 +4191,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>groundbaitId</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>窝料ID</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>低于此等级不可打窝。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -4201,17 +4213,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>costGoldPerUse</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>单次金币</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>打窝开始时扣除。</t>
+          <t>Overlay 显示名。</t>
         </is>
       </c>
     </row>
@@ -4223,17 +4235,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>castDurationMs</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>打窝等待毫秒</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>groundbaiting phase 时长。</t>
+          <t>低于此等级不可打窝。</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4257,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>durationMin</t>
+          <t>costGoldPerUse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>持续分钟</t>
+          <t>单次金币</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>与 maxBites 先到失效。</t>
+          <t>打窝开始时扣除。</t>
         </is>
       </c>
     </row>
@@ -4267,17 +4279,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>maxBites</t>
+          <t>castDurationMs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>持续口数</t>
+          <t>打窝等待毫秒</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>与 durationMin 先到失效。</t>
+          <t>groundbaiting phase 时长。</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4301,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>perStackBiteBonus</t>
+          <t>durationMin</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>每层咬钩参考</t>
+          <t>持续分钟</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>策划标注；实际用 maxBonus/stackK 曲线。</t>
+          <t>与 maxBites 先到失效。</t>
         </is>
       </c>
     </row>
@@ -4311,17 +4323,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>maxBonus</t>
+          <t>maxBites</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>咬钩加成渐近上限</t>
+          <t>持续口数</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>bonus=maxBonus*(1-exp(-stackK*stack))。</t>
+          <t>与 durationMin 先到失效。</t>
         </is>
       </c>
     </row>
@@ -4333,17 +4345,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>stackK</t>
+          <t>perStackBiteBonus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>曲线速率</t>
+          <t>每层咬钩参考</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>非线性叠层速率。</t>
+          <t>策划标注；实际用 maxBonus/stackK 曲线。</t>
         </is>
       </c>
     </row>
@@ -4355,17 +4367,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>sizeBonusPerStack</t>
+          <t>maxBonus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>尺寸每层增益m</t>
+          <t>咬钩加成渐近上限</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>临时，不写库。</t>
+          <t>bonus=maxBonus*(1-exp(-stackK*stack))。</t>
         </is>
       </c>
     </row>
@@ -4377,61 +4389,61 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>maxSizeBonus</t>
+          <t>stackK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>尺寸增益总帽m</t>
+          <t>曲线速率</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>临时 sizeBonus 上限。</t>
+          <t>非线性叠层速率。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>vesselId</t>
+          <t>sizeBonusPerStack</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>船具ID</t>
+          <t>尺寸每层增益m</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>临时，不写库。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>vessels</t>
+          <t>groundbaits</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>maxSizeBonus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>尺寸增益总帽m</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>商店显示名。</t>
+          <t>临时 sizeBonus 上限。</t>
         </is>
       </c>
     </row>
@@ -4443,17 +4455,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>unlockPlayerLevel</t>
+          <t>vesselId</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>解锁钓鱼等级</t>
+          <t>船具ID</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>低于此等级不能买。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -4465,17 +4477,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>priceGold</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>金币价格</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>一次性购入。</t>
+          <t>商店显示名。</t>
         </is>
       </c>
     </row>
@@ -4487,17 +4499,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>placeholderCatchCount</t>
+          <t>unlockPlayerLevel</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>占位捕捞次数</t>
+          <t>解锁钓鱼等级</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>表内预留，当前不生效。</t>
+          <t>低于此等级不能买。</t>
         </is>
       </c>
     </row>
@@ -4509,61 +4521,61 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>enabledUse</t>
+          <t>priceGold</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>是否允许使用</t>
+          <t>金币价格</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FALSE：可买但不可装备、不可开船。</t>
+          <t>一次性购入。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>clueId</t>
+          <t>placeholderCatchCount</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>线索ID</t>
+          <t>占位捕捞次数</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>唯一主键。</t>
+          <t>表内预留，当前不生效。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>spot_clue_texts</t>
+          <t>vessels</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>clueType</t>
+          <t>enabledUse</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>线索类型</t>
+          <t>是否允许使用</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
+          <t>FALSE：可买但不可装备、不可开船。</t>
         </is>
       </c>
     </row>
@@ -4575,17 +4587,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>clueText</t>
+          <t>clueId</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>线索文案</t>
+          <t>线索ID</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>坐席后聊天气泡展示的中文。</t>
+          <t>唯一主键。</t>
         </is>
       </c>
     </row>
@@ -4597,17 +4609,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>clueType</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>线索类型</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>加权随机相对权重，默认 1。</t>
+          <t>habitat 鱼喜环境 / activity 鱼情观察。</t>
         </is>
       </c>
     </row>
@@ -4619,17 +4631,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>clueText</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>最低钓鱼等级</t>
+          <t>线索文案</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>坐席后聊天气泡展示的中文。</t>
         </is>
       </c>
     </row>
@@ -4641,17 +4653,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>minPondLevel</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>最低塘熟练度</t>
+          <t>权重</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>未达到不进入抽选池。</t>
+          <t>加权随机相对权重，默认 1。</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4675,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>pondCategory</t>
+          <t>minPlayerLevel</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>塘分级过滤</t>
+          <t>最低钓鱼等级</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>空=全塘；否则仅匹配该分级。</t>
+          <t>未达到不进入抽选池。</t>
         </is>
       </c>
     </row>
@@ -4685,17 +4697,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>spotTag</t>
+          <t>minPondLevel</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>点位标签</t>
+          <t>最低塘熟练度</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>匹配 pond_spot_tags；空=不入池。</t>
+          <t>未达到不进入抽选池。</t>
         </is>
       </c>
     </row>
@@ -4707,17 +4719,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>activitySignal</t>
+          <t>pondCategory</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>鱼情信号档</t>
+          <t>塘分级过滤</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>habitat/active_high/active_mid/active_low/inactive/disturbed；供实时鱼群匹配。</t>
+          <t>空=全塘；否则仅匹配该分级。</t>
         </is>
       </c>
     </row>
@@ -4729,61 +4741,61 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>spotTag</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>点位标签</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>FALSE 不参与抽选。</t>
+          <t>匹配 pond_spot_tags；空=不入池。</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>spot_tag_defs</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>tagId</t>
+          <t>activitySignal</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>标签ID</t>
+          <t>鱼情信号档</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>habitat/active_high/active_mid/active_low/inactive/disturbed；供实时鱼群匹配。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>spot_tag_defs</t>
+          <t>spot_clue_texts</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>tagCategory</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>标签大类</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>terrain/water/light/wind/depth/shore。</t>
+          <t>FALSE 不参与抽选。</t>
         </is>
       </c>
     </row>
@@ -4795,17 +4807,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nameZh</t>
+          <t>tagId</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>标签ID</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>UI/策划显示。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -4817,61 +4829,61 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>descriptionZh</t>
+          <t>tagCategory</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>标签大类</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>标签含义参考。</t>
+          <t>terrain/water/light/wind/depth/shore。</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pond_spot_tags</t>
+          <t>spot_tag_defs</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>nameZh</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>鱼塘ID</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>与 ponds 对齐。</t>
+          <t>UI/策划显示。</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>pond_spot_tags</t>
+          <t>spot_tag_defs</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>spotId</t>
+          <t>descriptionZh</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>钓位ID</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>如 calm-spot-3。</t>
+          <t>标签含义参考。</t>
         </is>
       </c>
     </row>
@@ -4883,61 +4895,61 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>标签列表</t>
+          <t>鱼塘ID</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>逗号分隔多标签；每点 4–6 个跨类标签。</t>
+          <t>与 ponds 对齐。</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>achievements</t>
+          <t>pond_spot_tags</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>achievementId</t>
+          <t>spotId</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>成就ID</t>
+          <t>钓位ID</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>程序主键。</t>
+          <t>如 calm-spot-3。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>achievements</t>
+          <t>pond_spot_tags</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>标签列表</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>展示名。</t>
+          <t>逗号分隔多标签；每点 4–6 个跨类标签。</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4961,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>achievementId</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>成就ID</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>条件说明；隐藏成就未解锁时客户端不剧透。</t>
+          <t>程序主键。</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4983,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>iconKey</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>图标键</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>资源键。</t>
+          <t>展示名。</t>
         </is>
       </c>
     </row>
@@ -4993,17 +5005,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>catch/social/progress/album。</t>
+          <t>条件说明；隐藏成就未解锁时客户端不剧透。</t>
         </is>
       </c>
     </row>
@@ -5015,17 +5027,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>conditionType</t>
+          <t>iconKey</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>条件类型</t>
+          <t>图标键</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>catch_count/codex_count/return_count/max_size/album_pins。</t>
+          <t>资源键。</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5049,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>conditionValue</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>条件阈值</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>达标阈值。</t>
+          <t>catch/social/progress/album。</t>
         </is>
       </c>
     </row>
@@ -5059,17 +5071,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>sortOrder</t>
+          <t>conditionType</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>条件类型</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>展示序，小在前。</t>
+          <t>catch_count/codex_count/return_count/max_size/album_pins。</t>
         </is>
       </c>
     </row>
@@ -5081,15 +5093,59 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
+          <t>conditionValue</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>条件阈值</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>达标阈值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>sortOrder</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>展示序，小在前。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>achievements</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>isHidden</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>隐藏成就</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>TRUE：未解锁不展示条件。</t>
         </is>
@@ -13554,12 +13610,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13570,10 +13627,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>pondCategoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>spawnWeight</t>
         </is>
@@ -13587,10 +13649,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>塘类型中文名</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>品质</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>品质权重</t>
         </is>
@@ -13604,10 +13671,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>新手</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>38</v>
       </c>
     </row>
@@ -13619,10 +13691,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>新手</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -13634,10 +13711,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>38</v>
       </c>
     </row>
@@ -13649,10 +13731,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>28</v>
       </c>
     </row>
@@ -13664,10 +13751,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>18</v>
       </c>
     </row>
@@ -13679,10 +13771,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -13694,10 +13791,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13709,10 +13811,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13724,10 +13831,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13739,11 +13851,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>38</v>
+      <c r="D12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -13754,11 +13871,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>28</v>
+      <c r="D13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -13769,11 +13891,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>18</v>
+      <c r="D14" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -13784,11 +13911,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>11</v>
+      <c r="D15" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -13799,11 +13931,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>5</v>
+      <c r="D16" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -13814,11 +13951,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>2</v>
+      <c r="D17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -13829,11 +13971,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>老手</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="D18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -13844,11 +13991,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>32</v>
+      <c r="D19" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -13859,11 +14011,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>24</v>
+      <c r="D20" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -13874,11 +14031,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>15</v>
+      <c r="D21" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -13889,11 +14051,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>8</v>
+      <c r="D22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -13904,11 +14071,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>3</v>
+      <c r="D23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -13919,11 +14091,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>2</v>
+      <c r="D24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -13934,11 +14111,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>野外</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
+      <c r="D25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -13949,11 +14131,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>32</v>
+      <c r="D26" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="27">
@@ -13964,11 +14151,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>24</v>
+      <c r="D27" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -13979,11 +14171,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>15</v>
+      <c r="D28" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -13994,11 +14191,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>8</v>
+      <c r="D29" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -14009,11 +14211,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>3</v>
+      <c r="D30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -14024,11 +14231,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="D31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -14039,11 +14251,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>水库</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
+      <c r="D32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -14054,11 +14271,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>40</v>
+      <c r="D33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -14069,11 +14291,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>29</v>
+      <c r="D34" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -14084,11 +14311,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>19</v>
+      <c r="D35" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -14099,11 +14331,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>11</v>
+      <c r="D36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -14114,11 +14351,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>5</v>
+      <c r="D37" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -14129,11 +14371,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>3</v>
+      <c r="D38" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -14144,11 +14391,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
+      <c r="D39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -14159,10 +14411,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>44</v>
       </c>
     </row>
@@ -14174,10 +14431,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>32</v>
       </c>
     </row>
@@ -14189,10 +14451,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>21</v>
       </c>
     </row>
@@ -14204,10 +14471,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>purple</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>12</v>
       </c>
     </row>
@@ -14219,10 +14491,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>6</v>
       </c>
     </row>
@@ -14234,10 +14511,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14249,10 +14531,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>巨物</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14361,7 +14648,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C3" t="n">
         <v>0.05</v>
@@ -14388,7 +14675,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
       <c r="C4" t="n">
         <v>0.032</v>
@@ -14415,7 +14702,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C5" t="n">
         <v>0.018</v>
@@ -14442,7 +14729,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
         <v>0.008</v>
@@ -14469,7 +14756,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0.0035</v>
@@ -14496,7 +14783,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>0.0015</v>
@@ -14709,11 +14996,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>幼鱼出生/脱钩插值下限</t>
+          <t>幼鱼出生体长下限</t>
         </is>
       </c>
     </row>
@@ -14724,7 +15011,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14743,7 +15030,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.08m 幼鱼脱钩锚点</t>
+          <t>0.02m 幼鱼脱钩锚点</t>
         </is>
       </c>
     </row>
@@ -33846,13 +34133,13 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -33927,13 +34214,13 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -34008,13 +34295,13 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U5" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -34089,13 +34376,13 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U6" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -34170,13 +34457,13 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -34251,13 +34538,13 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U8" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -34332,13 +34619,13 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U9" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -34413,13 +34700,13 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U10" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -34494,13 +34781,13 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U11" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -34575,13 +34862,13 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U12" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -34656,13 +34943,13 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U13" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -34737,13 +35024,13 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U14" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -34818,13 +35105,13 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T15" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U15" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -34899,13 +35186,13 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U16" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -34980,13 +35267,13 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U17" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -35061,13 +35348,13 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U18" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -35142,13 +35429,13 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U19" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -35223,13 +35510,13 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U20" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -35304,13 +35591,13 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U21" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -35385,13 +35672,13 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -35462,13 +35749,13 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -35828,20 +36115,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35852,52 +36140,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>minSizeRatio</t>
+          <t>autoMinQuality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>minWeightJin</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>heavyWeightJin</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>maxSizeRatio</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>goldMulVsSell</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goldMulHeavy</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>playerXp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pondXp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sizeGainMinM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sizeGainMaxM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sizeGainMode</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>autoMinQuality</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>autoMinSizeRatio</t>
         </is>
       </c>
     </row>
@@ -35909,52 +36202,57 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>最小体长比</t>
+          <t>自动最低品质</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>最低体重斤</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>超重档斤</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>最大体长比</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>回鱼金倍率</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>超重回鱼倍率</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>玩家经验</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>鱼塘经验</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>增重下限m</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>增重上限m</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>增重模式</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>自动回鱼最低品质</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>自动回鱼最低体长比</t>
         </is>
       </c>
     </row>
@@ -35964,39 +36262,42 @@
           <t>purple</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.75</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>0.02</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>0.05</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>uniform_random</t>
         </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>purple</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -36292,7 +36593,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -36334,7 +36635,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -36376,7 +36677,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -36418,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -36460,7 +36761,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -36502,7 +36803,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -36544,7 +36845,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -36586,7 +36887,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -36628,7 +36929,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -36670,7 +36971,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -36712,7 +37013,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -36754,7 +37055,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -36796,7 +37097,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -36838,7 +37139,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -36880,7 +37181,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -36922,7 +37223,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -36964,7 +37265,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -37006,7 +37307,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -37048,7 +37349,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -37090,7 +37391,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -37132,7 +37433,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -37174,7 +37475,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -37216,7 +37517,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -37258,7 +37559,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -37300,7 +37601,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -37342,7 +37643,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -37384,7 +37685,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -37426,7 +37727,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -37468,7 +37769,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -37510,7 +37811,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -37552,7 +37853,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -37594,7 +37895,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -37636,7 +37937,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -37678,7 +37979,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -37720,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -37762,7 +38063,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -37804,7 +38105,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -37846,7 +38147,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -37888,7 +38189,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -37930,7 +38231,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -37972,7 +38273,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -38014,7 +38315,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -38098,7 +38399,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -38224,7 +38525,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -38266,7 +38567,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -38308,7 +38609,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -38350,7 +38651,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
